--- a/jpcore-r4/feature/swg2_servicerequest/StructureDefinition-jp-medicationrequest-injection.xlsx
+++ b/jpcore-r4/feature/swg2_servicerequest/StructureDefinition-jp-medicationrequest-injection.xlsx
@@ -1028,8 +1028,7 @@
     <t>What medication was supplied　医薬品</t>
   </si>
   <si>
-    <t>Identifies the medication that was administered. This is either a link to a resource representing the details of the medication or a simple attribute carrying a code that identifies the medication from a known list of medications.  
-投与された薬剤を識別する。既知の薬のリストから薬を識別するコード情報を設定する。</t>
+    <t>医薬品の識別情報は必須でありmedicationReference.referenceが必ず存在しなければならない、JP Coreでは注射の医薬品情報は単一薬剤の場合も Medicationリソースとして記述し、medicationCodeableConceptは使用しない。参照するMedicationリソースは、MedicationRequest.contained属性に内包することが望ましいが、外部参照としても良い。</t>
   </si>
   <si>
     <t>If only a code is specified, then it needs to be a code for a specific product. If more information is required, then the use of the medication resource is recommended.  For example, if you require form or lot number, then you must reference the Medication resource.  
